--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DA0360-8FF9-43CA-9C55-A0A6EE758A3D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F815B00E-7795-4CF9-809A-DF0BC3B1296D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -183,19 +183,29 @@
   </si>
   <si>
     <t>Application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{users:Automation_SPI} </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -218,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -226,6 +236,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -577,8 +590,8 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F815B00E-7795-4CF9-809A-DF0BC3B1296D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57099476-58A1-4B53-A674-DC8BB636FE8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
     <t>Application</t>
   </si>
   <si>
-    <t xml:space="preserve">{users:Automation_SPI} </t>
+    <t>Debra Clements</t>
   </si>
 </sst>
 </file>
@@ -732,8 +732,8 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
+      <c r="C3" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -915,7 +915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -928,6 +928,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57099476-58A1-4B53-A674-DC8BB636FE8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790A95E7-F357-4AA7-8402-5527E086AC14}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="52">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -186,13 +186,16 @@
   </si>
   <si>
     <t>Debra Clements</t>
+  </si>
+  <si>
+    <t>SPI Automation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,6 +209,21 @@
       <color rgb="FF297BDE"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -225,10 +243,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -240,8 +259,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -590,8 +611,8 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>50</v>
+      <c r="C3" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -617,7 +638,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" tooltip="SPI Automation" display="https://lsc--qa--c.visualforce.com/0030r00000KHDtmAAH" xr:uid="{6814200E-93A7-427B-A890-858C6DF817D4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790A95E7-F357-4AA7-8402-5527E086AC14}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D916F7FC-A154-4C74-86DB-ED77D70E9D0B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -183,9 +183,6 @@
   </si>
   <si>
     <t>Application</t>
-  </si>
-  <si>
-    <t>Debra Clements</t>
   </si>
   <si>
     <t>SPI Automation</t>
@@ -612,7 +609,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9582B3DC-C297-46D0-981C-ACA6E6B6CDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B49B7D-01D6-4385-8039-BF19FFC32E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="53">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -170,40 +170,28 @@
     <t>Automation SPI3</t>
   </si>
   <si>
-    <t>fieldTitle__c</t>
-  </si>
-  <si>
-    <t>fieldVisitDateandTime__c</t>
-  </si>
-  <si>
-    <t>fieldVisitEndDateTime__c</t>
-  </si>
-  <si>
-    <t>fieldDescription__c</t>
-  </si>
-  <si>
-    <t>fieldPointsdiscussedwithofficials__c</t>
-  </si>
-  <si>
-    <t>fieldSiteVisitPurpose__c</t>
-  </si>
-  <si>
-    <t>fieldSourceSiteVisit__c</t>
-  </si>
-  <si>
-    <t>fieldSupportingCommentsQuestion1__c</t>
-  </si>
-  <si>
-    <t>fieldGranteePOCContact__c</t>
-  </si>
-  <si>
-    <t>fieldSiteVisitType__c</t>
-  </si>
-  <si>
-    <t>fieldMonitoringType__c</t>
-  </si>
-  <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>VisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>VisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Pointsdiscussedwithofficials__c</t>
+  </si>
+  <si>
+    <t>SiteVisitPurpose__c</t>
+  </si>
+  <si>
+    <t>SourceSiteVisit__c</t>
+  </si>
+  <si>
+    <t>SupportingCommentsQuestion1__c</t>
   </si>
 </sst>
 </file>
@@ -245,8 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -570,57 +557,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -639,67 +626,65 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7BC2C8-C330-4CF5-B350-FDF7466963B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -710,66 +695,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5711-50C5-4AD1-966A-EEB6DD06A5CB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -781,61 +764,61 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -847,98 +830,98 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -950,77 +933,76 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1032,66 +1014,64 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1103,66 +1083,64 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1174,25 +1152,25 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
-    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.26953125" customWidth="1"/>
+    <col min="3" max="3" width="100.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1203,8 +1181,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
@@ -1214,8 +1192,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
@@ -1225,8 +1203,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -1236,8 +1214,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
@@ -1247,8 +1225,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
@@ -1258,8 +1236,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
@@ -1269,8 +1247,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9" t="s">
@@ -1280,8 +1258,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>4</v>
       </c>
       <c r="B10" t="s">

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B49B7D-01D6-4385-8039-BF19FFC32E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2571F03D-5F6C-4C2C-866E-9C0E39C596A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="8" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -260,9 +260,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -300,7 +300,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -406,7 +406,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -548,7 +548,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -557,13 +557,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +574,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -585,7 +585,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -596,7 +596,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -607,7 +607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -626,13 +626,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7BC2C8-C330-4CF5-B350-FDF7466963B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,7 +643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -654,7 +654,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -665,7 +665,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -676,7 +676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -695,13 +695,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5711-50C5-4AD1-966A-EEB6DD06A5CB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -712,7 +712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -723,7 +723,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -745,7 +745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -764,13 +764,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -778,7 +778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -786,7 +786,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -794,7 +794,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -802,22 +802,22 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>19</v>
       </c>
@@ -830,14 +830,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -848,7 +848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -859,7 +859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -870,7 +870,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -881,7 +881,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -892,7 +892,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -903,7 +903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -914,7 +914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -933,14 +933,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -973,7 +973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -984,7 +984,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -995,7 +995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1014,13 +1014,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1083,13 +1083,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1152,14 +1152,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.26953125" customWidth="1"/>
-    <col min="3" max="3" width="100.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>

--- a/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
+++ b/src/main/resources/Organizational_DeskReview_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA Org 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2571F03D-5F6C-4C2C-866E-9C0E39C596A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EC8A38-C00A-40D9-BC6D-C032CFB8659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="8" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="54">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>SupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>Deshka Kostova</t>
   </si>
 </sst>
 </file>
@@ -557,13 +560,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -585,7 +588,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -593,10 +596,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -607,7 +610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -626,13 +629,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7BC2C8-C330-4CF5-B350-FDF7466963B4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,7 +646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -654,7 +657,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -665,7 +668,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -676,7 +679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -695,13 +698,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661F5711-50C5-4AD1-966A-EEB6DD06A5CB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -712,7 +715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -723,7 +726,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -734,7 +737,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -745,7 +748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -764,13 +767,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -778,7 +781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -786,7 +789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -794,7 +797,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -802,22 +805,22 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>19</v>
       </c>
@@ -830,14 +833,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -848,7 +851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -859,7 +862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -870,7 +873,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -881,7 +884,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -892,7 +895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -903,7 +906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -914,7 +917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -933,14 +936,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F1479-2E59-4670-8557-FD1A600D9DD9}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -962,7 +965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -973,7 +976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -984,7 +987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -995,7 +998,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1014,13 +1017,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172EB3BB-E440-4D9F-AB45-F40BA5013EFF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1045,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1053,7 +1056,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1083,13 +1086,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0A2D9-C8FF-4F2E-9357-11D1A04AB716}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1100,7 +1103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1111,7 +1114,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1122,7 +1125,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1133,7 +1136,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1152,14 +1155,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
-    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" customWidth="1"/>
+    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1170,7 +1173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1181,7 +1184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1203,7 +1206,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1214,7 +1217,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1225,7 +1228,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1236,7 +1239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1247,7 +1250,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1258,7 +1261,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
